--- a/tests/perf_v2/perf_history/v2.4.2/multi_label_cls/MULTI_LABEL_CLS-raw-multilabel_tiny_bccd.xlsx
+++ b/tests/perf_v2/perf_history/v2.4.2/multi_label_cls/MULTI_LABEL_CLS-raw-multilabel_tiny_bccd.xlsx
@@ -586,7 +586,7 @@
         <v>54</v>
       </c>
       <c r="C2" t="n">
-        <v>15.11731696128845</v>
+        <v>13.72611927986145</v>
       </c>
       <c r="D2" t="n">
         <v>0.8100000023841858</v>
@@ -604,32 +604,32 @@
         <v>0.8266666531562805</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0508685465212221</v>
+        <v>0.0511802655679207</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0175328534096479</v>
+        <v>0.0174517910927534</v>
       </c>
       <c r="K2" t="n">
-        <v>7.567425489425659</v>
+        <v>7.35471248626709</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0170003795623779</v>
+        <v>0.0149469518661499</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0256399250030517</v>
+        <v>0.0257219243049621</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0387802648544311</v>
+        <v>0.0374325990676879</v>
       </c>
       <c r="O2" t="n">
-        <v>2.563992500305176</v>
+        <v>2.572192430496216</v>
       </c>
       <c r="P2" t="n">
-        <v>3.878026485443115</v>
+        <v>3.743259906768799</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-125014</t>
+          <t>20250714-172010</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -674,13 +674,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -690,7 +692,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -702,10 +704,10 @@
         <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>15.5703136920929</v>
+        <v>13.73824524879456</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7900000214576721</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="E3" t="n">
         <v>0.9444444179534912</v>
@@ -720,32 +722,32 @@
         <v>0.8266666531562805</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0529132419162325</v>
+        <v>0.0520614827120745</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0145177459344267</v>
+        <v>0.0172190573066473</v>
       </c>
       <c r="K3" t="n">
-        <v>7.582718372344971</v>
+        <v>7.589781999588013</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0166418576240539</v>
+        <v>0.0152278852462768</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0251703238487243</v>
+        <v>0.0245030689239501</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0370665836334228</v>
+        <v>0.0362727737426757</v>
       </c>
       <c r="O3" t="n">
-        <v>2.517032384872437</v>
+        <v>2.45030689239502</v>
       </c>
       <c r="P3" t="n">
-        <v>3.706658363342285</v>
+        <v>3.627277374267578</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-125113</t>
+          <t>20250714-172103</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -790,13 +792,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -806,7 +810,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -818,7 +822,7 @@
         <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>15.24557089805603</v>
+        <v>13.72276782989502</v>
       </c>
       <c r="D4" t="n">
         <v>0.8100000023841858</v>
@@ -836,32 +840,32 @@
         <v>0.8266666531562805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0523923812089142</v>
+        <v>0.0506152885931509</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0220337100327014</v>
+        <v>0.0174798592925071</v>
       </c>
       <c r="K4" t="n">
-        <v>7.387991666793823</v>
+        <v>7.346804857254028</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0184694266319274</v>
+        <v>0.0150599384307861</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0251912069320678</v>
+        <v>0.0251725363731384</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0368739557266235</v>
+        <v>0.0365570592880249</v>
       </c>
       <c r="O4" t="n">
-        <v>2.519120693206787</v>
+        <v>2.517253637313843</v>
       </c>
       <c r="P4" t="n">
-        <v>3.687395572662354</v>
+        <v>3.65570592880249</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-125211</t>
+          <t>20250714-172156</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -906,13 +910,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -922,7 +928,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -934,50 +940,50 @@
         <v>54</v>
       </c>
       <c r="C5" t="n">
-        <v>14.87276148796082</v>
+        <v>14.32102131843567</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="E5" t="n">
         <v>0.9444444179534912</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="H5" t="n">
         <v>0.8266666531562805</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0533057451248168</v>
+        <v>0.0518323492120813</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0150455283001065</v>
+        <v>0.0141438199207186</v>
       </c>
       <c r="K5" t="n">
-        <v>8.024777173995972</v>
+        <v>7.296021938323975</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0169680047035217</v>
+        <v>0.0156718325614929</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0251883339881896</v>
+        <v>0.0247092747688293</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0378026008605957</v>
+        <v>0.0379553365707397</v>
       </c>
       <c r="O5" t="n">
-        <v>2.51883339881897</v>
+        <v>2.470927476882935</v>
       </c>
       <c r="P5" t="n">
-        <v>3.780260086059569</v>
+        <v>3.795533657073975</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-125309</t>
+          <t>20250714-172249</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1022,13 +1028,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1038,7 +1046,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1050,10 +1058,10 @@
         <v>54</v>
       </c>
       <c r="C6" t="n">
-        <v>15.38679194450378</v>
+        <v>14.04335999488831</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7900000214576721</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="E6" t="n">
         <v>0.9444444179534912</v>
@@ -1068,32 +1076,32 @@
         <v>0.8266666531562805</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0525271230273776</v>
+        <v>0.0519438628797177</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0147088905796408</v>
+        <v>0.017417898401618</v>
       </c>
       <c r="K6" t="n">
-        <v>7.834366798400879</v>
+        <v>7.473477363586426</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0171483349800109</v>
+        <v>0.0149555397033691</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0258867096900939</v>
+        <v>0.0254077863693237</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0374405884742736</v>
+        <v>0.0362944102287292</v>
       </c>
       <c r="O6" t="n">
-        <v>2.588670969009399</v>
+        <v>2.540778636932373</v>
       </c>
       <c r="P6" t="n">
-        <v>3.744058847427368</v>
+        <v>3.629441022872925</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-125407</t>
+          <t>20250714-172343</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1138,13 +1146,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1154,7 +1164,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1324,53 +1334,53 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C2" t="n">
-        <v>19.12436151504517</v>
+        <v>14.35491275787354</v>
       </c>
       <c r="D2" t="n">
         <v>1.669999957084656</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.9444444179534912</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8233333230018616</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="G2" t="n">
         <v>0.8266666531562805</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8500000238418579</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0694003485251163</v>
+        <v>0.0695992752357765</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0795258805155754</v>
+        <v>0.0606473907828331</v>
       </c>
       <c r="K2" t="n">
-        <v>5.477615833282471</v>
+        <v>5.275290489196777</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0174576377868652</v>
+        <v>0.014866464138031</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0214855408668518</v>
+        <v>0.0219147586822509</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0269442892074584</v>
+        <v>0.0289610147476196</v>
       </c>
       <c r="O2" t="n">
-        <v>2.148554086685181</v>
+        <v>2.191475868225098</v>
       </c>
       <c r="P2" t="n">
-        <v>2.69442892074585</v>
+        <v>2.896101474761963</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-101131</t>
+          <t>20250714-145907</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -1415,13 +1425,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1431,7 +1443,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1440,53 +1452,53 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>22.13289499282837</v>
+        <v>15.05145788192749</v>
       </c>
       <c r="D3" t="n">
         <v>1.669999957084656</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.9444444179534912</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8066666722297668</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8033333420753479</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07149871693381769</v>
+        <v>0.07223637015731239</v>
       </c>
       <c r="J3" t="n">
-        <v>0.081345185637474</v>
+        <v>0.0609645545482635</v>
       </c>
       <c r="K3" t="n">
-        <v>5.523385763168335</v>
+        <v>5.344091176986694</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0177712082862854</v>
+        <v>0.015126609802246</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0209679222106933</v>
+        <v>0.0213051152229309</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0285278487205505</v>
+        <v>0.0284539127349853</v>
       </c>
       <c r="O3" t="n">
-        <v>2.096792221069336</v>
+        <v>2.130511522293091</v>
       </c>
       <c r="P3" t="n">
-        <v>2.852784872055054</v>
+        <v>2.845391273498535</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-101228</t>
+          <t>20250714-145956</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1531,13 +1543,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1547,7 +1561,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1556,53 +1570,53 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>16.494873046875</v>
+        <v>14.62763833999634</v>
       </c>
       <c r="D4" t="n">
-        <v>1.669999957084656</v>
+        <v>1.700000047683716</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8399999737739563</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0669881731776867</v>
+        <v>0.068606208871912</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0769879221916198</v>
+        <v>0.0673769265413284</v>
       </c>
       <c r="K4" t="n">
-        <v>5.662561655044556</v>
+        <v>5.391050815582275</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0195293927192688</v>
+        <v>0.0154531574249267</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0210012555122375</v>
+        <v>0.0223523473739624</v>
       </c>
       <c r="N4" t="n">
-        <v>0.028641664981842</v>
+        <v>0.0273227000236511</v>
       </c>
       <c r="O4" t="n">
-        <v>2.100125551223755</v>
+        <v>2.23523473739624</v>
       </c>
       <c r="P4" t="n">
-        <v>2.864166498184204</v>
+        <v>2.732270002365112</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-101329</t>
+          <t>20250714-150045</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1647,13 +1661,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1663,7 +1679,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1672,53 +1688,53 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="C5" t="n">
-        <v>22.23809242248535</v>
+        <v>14.52314186096191</v>
       </c>
       <c r="D5" t="n">
         <v>1.669999957084656</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.9444444179534912</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8166666626930237</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07130400440360921</v>
+        <v>0.06890621891728151</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0795830637216568</v>
+        <v>0.0612755492329597</v>
       </c>
       <c r="K5" t="n">
-        <v>5.737540245056152</v>
+        <v>5.294822216033936</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0179733085632324</v>
+        <v>0.0150845742225646</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0221245551109313</v>
+        <v>0.0220088696479797</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0280822539329528</v>
+        <v>0.027623438835144</v>
       </c>
       <c r="O5" t="n">
-        <v>2.21245551109314</v>
+        <v>2.200886964797974</v>
       </c>
       <c r="P5" t="n">
-        <v>2.808225393295288</v>
+        <v>2.762343883514404</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-101425</t>
+          <t>20250714-150135</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1763,13 +1779,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1779,7 +1797,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1788,53 +1806,53 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C6" t="n">
-        <v>16.858558177948</v>
+        <v>19.32826638221741</v>
       </c>
       <c r="D6" t="n">
-        <v>1.669999957084656</v>
+        <v>1.700000047683716</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.8233333230018616</v>
       </c>
       <c r="H6" t="n">
         <v>0.8266666531562805</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06912783444938</v>
+        <v>0.06890149374265921</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07982528954744331</v>
+        <v>0.0648494064807891</v>
       </c>
       <c r="K6" t="n">
-        <v>5.680513620376587</v>
+        <v>5.198547840118408</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0198182940483093</v>
+        <v>0.0147631669044494</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0222601985931396</v>
+        <v>0.0213582134246826</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0270341181755065</v>
+        <v>0.0279341721534729</v>
       </c>
       <c r="O6" t="n">
-        <v>2.226019859313965</v>
+        <v>2.135821342468262</v>
       </c>
       <c r="P6" t="n">
-        <v>2.703411817550659</v>
+        <v>2.79341721534729</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-101526</t>
+          <t>20250714-150224</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1879,13 +1897,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1895,7 +1915,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2088,7 @@
         <v>54</v>
       </c>
       <c r="C2" t="n">
-        <v>20.66032409667969</v>
+        <v>19.35611176490784</v>
       </c>
       <c r="D2" t="n">
         <v>2.430000066757202</v>
@@ -2077,7 +2097,7 @@
         <v>0.9444444179534912</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8266666531562805</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="G2" t="n">
         <v>0.8266666531562805</v>
@@ -2086,32 +2106,32 @@
         <v>0.8266666531562805</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1014513351299144</v>
+        <v>0.0952216519249809</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0962041765451431</v>
+        <v>0.0676127970218658</v>
       </c>
       <c r="K2" t="n">
-        <v>15.11453557014465</v>
+        <v>13.5654923915863</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0282089161872863</v>
+        <v>0.0316924691200256</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0325735425949096</v>
+        <v>0.0357282900810241</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0444192504882812</v>
+        <v>0.0411410641670227</v>
       </c>
       <c r="O2" t="n">
-        <v>3.257354259490967</v>
+        <v>3.572829008102417</v>
       </c>
       <c r="P2" t="n">
-        <v>4.441925048828125</v>
+        <v>4.114106416702271</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-105859</t>
+          <t>20250714-154002</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -2156,13 +2176,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -2172,7 +2194,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2206,7 @@
         <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>20.98583841323853</v>
+        <v>19.46431875228882</v>
       </c>
       <c r="D3" t="n">
         <v>2.430000066757202</v>
@@ -2202,32 +2224,32 @@
         <v>0.8266666531562805</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1022669076919555</v>
+        <v>0.0967137769416526</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0788644105195999</v>
+        <v>0.0715500935912132</v>
       </c>
       <c r="K3" t="n">
-        <v>15.15573883056641</v>
+        <v>13.41577768325806</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0284727501869201</v>
+        <v>0.0330884432792663</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0330030035972595</v>
+        <v>0.0351034569740295</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0431388354301452</v>
+        <v>0.0419417381286621</v>
       </c>
       <c r="O3" t="n">
-        <v>3.300300359725952</v>
+        <v>3.510345697402954</v>
       </c>
       <c r="P3" t="n">
-        <v>4.313883543014526</v>
+        <v>4.194173812866211</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-110024</t>
+          <t>20250714-154125</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -2272,13 +2294,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -2288,7 +2312,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2324,7 @@
         <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>20.90217971801757</v>
+        <v>19.79498362541199</v>
       </c>
       <c r="D4" t="n">
         <v>2.430000066757202</v>
@@ -2318,32 +2342,32 @@
         <v>0.8266666531562805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1018457412719726</v>
+        <v>0.09668568328574841</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0918215066194534</v>
+        <v>0.0675332620739936</v>
       </c>
       <c r="K4" t="n">
-        <v>14.69458794593811</v>
+        <v>13.38599038124084</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0279991316795349</v>
+        <v>0.0325097680091857</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0337356114387512</v>
+        <v>0.0326925611495971</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0488217854499816</v>
+        <v>0.0424235987663269</v>
       </c>
       <c r="O4" t="n">
-        <v>3.373561143875122</v>
+        <v>3.269256114959717</v>
       </c>
       <c r="P4" t="n">
-        <v>4.882178544998169</v>
+        <v>4.24235987663269</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-110149</t>
+          <t>20250714-154248</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -2388,13 +2412,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2404,7 +2430,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2442,7 @@
         <v>54</v>
       </c>
       <c r="C5" t="n">
-        <v>20.89844536781311</v>
+        <v>19.85691118240356</v>
       </c>
       <c r="D5" t="n">
         <v>2.430000066757202</v>
@@ -2434,32 +2460,32 @@
         <v>0.8266666531562805</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1035060661810415</v>
+        <v>0.0968298293926097</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0792497619986534</v>
+        <v>0.07204625010490411</v>
       </c>
       <c r="K5" t="n">
-        <v>14.80789256095886</v>
+        <v>13.46007227897644</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0281074357032775</v>
+        <v>0.032745726108551</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0329922652244567</v>
+        <v>0.0337011051177978</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0447259593009948</v>
+        <v>0.0418956184387207</v>
       </c>
       <c r="O5" t="n">
-        <v>3.299226522445679</v>
+        <v>3.370110511779785</v>
       </c>
       <c r="P5" t="n">
-        <v>4.472595930099487</v>
+        <v>4.18956184387207</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-110314</t>
+          <t>20250714-154411</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -2504,13 +2530,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2520,7 +2548,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2560,7 @@
         <v>54</v>
       </c>
       <c r="C6" t="n">
-        <v>20.96876454353333</v>
+        <v>19.88966727256775</v>
       </c>
       <c r="D6" t="n">
         <v>2.430000066757202</v>
@@ -2550,32 +2578,32 @@
         <v>0.8266666531562805</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1044785799803556</v>
+        <v>0.0955410930845472</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0752381235361099</v>
+        <v>0.0735162273049354</v>
       </c>
       <c r="K6" t="n">
-        <v>16.00159597396851</v>
+        <v>13.50002455711365</v>
       </c>
       <c r="L6" t="n">
-        <v>0.028562593460083</v>
+        <v>0.0332831311225891</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0329775381088256</v>
+        <v>0.0313347649574279</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0450392627716064</v>
+        <v>0.0420799398422241</v>
       </c>
       <c r="O6" t="n">
-        <v>3.297753810882568</v>
+        <v>3.133476495742798</v>
       </c>
       <c r="P6" t="n">
-        <v>4.503926277160645</v>
+        <v>4.207993984222412</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-110439</t>
+          <t>20250714-154535</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -2620,13 +2648,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2636,7 +2666,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2809,10 +2839,10 @@
         <v>54</v>
       </c>
       <c r="C2" t="n">
-        <v>15.2288007736206</v>
+        <v>14.52906203269958</v>
       </c>
       <c r="D2" t="n">
-        <v>1.049999952316284</v>
+        <v>0.9700000286102296</v>
       </c>
       <c r="E2" t="n">
         <v>0.9444444179534912</v>
@@ -2827,32 +2857,32 @@
         <v>0.8266666531562805</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0612599452336628</v>
+        <v>0.0604555739296806</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0531481839716434</v>
+        <v>0.0450151078402996</v>
       </c>
       <c r="K2" t="n">
-        <v>6.19593358039856</v>
+        <v>5.787055492401123</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0131835269927978</v>
+        <v>0.0117847895622253</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0225378537178039</v>
+        <v>0.022358820438385</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0277945470809936</v>
+        <v>0.0256759214401245</v>
       </c>
       <c r="O2" t="n">
-        <v>2.253785371780396</v>
+        <v>2.235882043838501</v>
       </c>
       <c r="P2" t="n">
-        <v>2.779454708099365</v>
+        <v>2.567592144012451</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-120537</t>
+          <t>20250714-164337</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -2897,13 +2927,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -2913,7 +2945,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2925,50 +2957,50 @@
         <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>15.37757349014282</v>
+        <v>14.6276044845581</v>
       </c>
       <c r="D3" t="n">
-        <v>1.049999952316284</v>
+        <v>0.9700000286102296</v>
       </c>
       <c r="E3" t="n">
         <v>0.9444444179534912</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8166666626930237</v>
+        <v>0.8266666531562805</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06258792347378191</v>
+        <v>0.0602375887058399</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0514871701598167</v>
+        <v>0.0473618619143962</v>
       </c>
       <c r="K3" t="n">
-        <v>5.886424064636231</v>
+        <v>5.781199932098389</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0128803944587707</v>
+        <v>0.0113629984855651</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0214445257186889</v>
+        <v>0.0208402466773986</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0274428868293762</v>
+        <v>0.0263406085968017</v>
       </c>
       <c r="O3" t="n">
-        <v>2.144452571868896</v>
+        <v>2.084024667739868</v>
       </c>
       <c r="P3" t="n">
-        <v>2.744288682937622</v>
+        <v>2.634060859680176</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-120629</t>
+          <t>20250714-164425</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -3013,13 +3045,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -3029,7 +3063,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3075,7 @@
         <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>15.28306269645691</v>
+        <v>14.29548025131226</v>
       </c>
       <c r="D4" t="n">
         <v>0.9700000286102296</v>
@@ -3050,41 +3084,41 @@
         <v>0.9444444179534912</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8133333325386047</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="G4" t="n">
         <v>0.8266666531562805</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.8233333230018616</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0616019875914961</v>
+        <v>0.0615256274188005</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0620597451925277</v>
+        <v>0.0441161170601844</v>
       </c>
       <c r="K4" t="n">
-        <v>5.979319334030151</v>
+        <v>5.661892414093018</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0131055235862731</v>
+        <v>0.0112053561210632</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0221422028541564</v>
+        <v>0.0218978762626647</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0279035687446594</v>
+        <v>0.0258294749259948</v>
       </c>
       <c r="O4" t="n">
-        <v>2.214220285415649</v>
+        <v>2.189787626266479</v>
       </c>
       <c r="P4" t="n">
-        <v>2.790356874465942</v>
+        <v>2.582947492599488</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-120721</t>
+          <t>20250714-164513</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -3129,13 +3163,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -3145,7 +3181,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -3157,10 +3193,10 @@
         <v>54</v>
       </c>
       <c r="C5" t="n">
-        <v>15.67039036750794</v>
+        <v>14.48665118217468</v>
       </c>
       <c r="D5" t="n">
-        <v>1.019999980926514</v>
+        <v>0.9700000286102296</v>
       </c>
       <c r="E5" t="n">
         <v>0.9444444179534912</v>
@@ -3169,38 +3205,38 @@
         <v>0.8266666531562805</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8266666531562805</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8266666531562805</v>
+        <v>0.8166666626930237</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0624577160234804</v>
+        <v>0.062582978495845</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0517123490571975</v>
+        <v>0.044122640043497</v>
       </c>
       <c r="K5" t="n">
-        <v>5.874925136566162</v>
+        <v>5.784684896469116</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0125812363624572</v>
+        <v>0.0113609266281127</v>
       </c>
       <c r="M5" t="n">
-        <v>0.022436876296997</v>
+        <v>0.0226572489738464</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0269907569885253</v>
+        <v>0.0264738726615905</v>
       </c>
       <c r="O5" t="n">
-        <v>2.243687629699707</v>
+        <v>2.265724897384644</v>
       </c>
       <c r="P5" t="n">
-        <v>2.699075698852539</v>
+        <v>2.647387266159058</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-120814</t>
+          <t>20250714-164600</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -3245,13 +3281,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -3261,7 +3299,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3311,7 @@
         <v>54</v>
       </c>
       <c r="C6" t="n">
-        <v>15.28831911087036</v>
+        <v>14.37325358390808</v>
       </c>
       <c r="D6" t="n">
         <v>0.9700000286102296</v>
@@ -3291,32 +3329,32 @@
         <v>0.8266666531562805</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0603604625772546</v>
+        <v>0.0612680735411466</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0471203327178955</v>
+        <v>0.0487944595515728</v>
       </c>
       <c r="K6" t="n">
-        <v>5.890030860900879</v>
+        <v>5.767318964004517</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0131569218635559</v>
+        <v>0.0119395637512207</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0222587800025939</v>
+        <v>0.0217382454872131</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0274829697608947</v>
+        <v>0.0251616692543029</v>
       </c>
       <c r="O6" t="n">
-        <v>2.225878000259399</v>
+        <v>2.173824548721313</v>
       </c>
       <c r="P6" t="n">
-        <v>2.748296976089477</v>
+        <v>2.516166925430298</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-120906</t>
+          <t>20250714-164648</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -3361,13 +3399,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -3377,7 +3417,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
